--- a/E/DU6AMKT.xlsx
+++ b/E/DU6AMKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="26">
   <si>
     <t/>
   </si>
   <si>
-    <t>20135313</t>
-  </si>
-  <si>
-    <t>WOW SPAGHETI BOLOG76</t>
+    <t>20139772</t>
+  </si>
+  <si>
+    <t>BRIO POTATO BBQ 49G</t>
   </si>
   <si>
     <t>DU6AMKT</t>
@@ -31,58 +31,61 @@
     <t>RT,(E-1B)</t>
   </si>
   <si>
-    <t>20135312</t>
-  </si>
-  <si>
-    <t>WOW SPAGHETI CARB80</t>
+    <t>20046434</t>
+  </si>
+  <si>
+    <t>BRIO POTATO BISC 56G</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
-    <t>20137860</t>
-  </si>
-  <si>
-    <t>WOW AGLI OLIO 75G</t>
+    <t>20045178</t>
+  </si>
+  <si>
+    <t>SAFE/C MNYK ANGIN 10</t>
   </si>
   <si>
     <t>3</t>
   </si>
   <si>
-    <t>20134841</t>
-  </si>
-  <si>
-    <t>CUSSONS TELON PLS 60</t>
+    <t>RT,(E-4B)</t>
+  </si>
+  <si>
+    <t>20102037</t>
+  </si>
+  <si>
+    <t>SAFE/C MYK AGN STR10</t>
   </si>
   <si>
     <t>4</t>
   </si>
   <si>
+    <t>20096777</t>
+  </si>
+  <si>
+    <t>WHISKAS OCEAN FSH 80</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
     <t>RT,(E-3B)</t>
   </si>
   <si>
-    <t>20083934</t>
-  </si>
-  <si>
-    <t>KOJIESAN SL SOAP 65</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>20083935</t>
-  </si>
-  <si>
-    <t>KOJIESAN DW SOAP 65</t>
+    <t>20031233</t>
+  </si>
+  <si>
+    <t>WHISKAS CF MAC&amp;SAL80</t>
   </si>
   <si>
     <t>6</t>
   </si>
   <si>
-    <t>20128963</t>
-  </si>
-  <si>
-    <t>KJSAN SL SOAP HDRO65</t>
+    <t>20031238</t>
+  </si>
+  <si>
+    <t>WHISKAS JR MCKRL 80</t>
   </si>
   <si>
     <t>7</t>
@@ -564,15 +567,15 @@
         <v>11</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>3</v>
@@ -581,10 +584,10 @@
         <v>4</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -604,15 +607,15 @@
         <v>18</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>3</v>
@@ -621,18 +624,18 @@
         <v>4</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>3</v>
@@ -641,10 +644,10 @@
         <v>4</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>

--- a/E/DU6AMKT.xlsx
+++ b/E/DU6AMKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="27">
   <si>
     <t/>
   </si>
   <si>
-    <t>20139772</t>
-  </si>
-  <si>
-    <t>BRIO POTATO BBQ 49G</t>
+    <t>10022534</t>
+  </si>
+  <si>
+    <t>ABC KCP MNS PCH685G</t>
   </si>
   <si>
     <t>DU6AMKT</t>
@@ -28,67 +28,70 @@
     <t>1</t>
   </si>
   <si>
-    <t>RT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20046434</t>
-  </si>
-  <si>
-    <t>BRIO POTATO BISC 56G</t>
+    <t>RT,(E-2B)</t>
+  </si>
+  <si>
+    <t>10004336</t>
+  </si>
+  <si>
+    <t>INDOMARET AIR MIN600</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
-    <t>20045178</t>
-  </si>
-  <si>
-    <t>SAFE/C MNYK ANGIN 10</t>
+    <t>PT,(E-1H)</t>
+  </si>
+  <si>
+    <t>10008882</t>
+  </si>
+  <si>
+    <t>K/API KOPI SPCL 150G</t>
+  </si>
+  <si>
+    <t>RT,(E-4B)</t>
+  </si>
+  <si>
+    <t>20084481</t>
+  </si>
+  <si>
+    <t>POP MIE PD.DWR AYM75</t>
   </si>
   <si>
     <t>3</t>
   </si>
   <si>
-    <t>RT,(E-4B)</t>
-  </si>
-  <si>
-    <t>20102037</t>
-  </si>
-  <si>
-    <t>SAFE/C MYK AGN STR10</t>
+    <t>20091304</t>
+  </si>
+  <si>
+    <t>POP MIE PD.GLD AYM75</t>
   </si>
   <si>
     <t>4</t>
   </si>
   <si>
-    <t>20096777</t>
-  </si>
-  <si>
-    <t>WHISKAS OCEAN FSH 80</t>
+    <t>20140188</t>
+  </si>
+  <si>
+    <t>POP MI KARI LAVA 79G</t>
   </si>
   <si>
     <t>5</t>
   </si>
   <si>
-    <t>RT,(E-3B)</t>
-  </si>
-  <si>
-    <t>20031233</t>
-  </si>
-  <si>
-    <t>WHISKAS CF MAC&amp;SAL80</t>
+    <t>20140189</t>
+  </si>
+  <si>
+    <t>POP MI BASO GRNT 77G</t>
+  </si>
+  <si>
+    <t>20024079</t>
+  </si>
+  <si>
+    <t>TELUR AYM NEGERI BKL</t>
   </si>
   <si>
     <t>6</t>
-  </si>
-  <si>
-    <t>20031238</t>
-  </si>
-  <si>
-    <t>WHISKAS JR MCKRL 80</t>
-  </si>
-  <si>
-    <t>7</t>
   </si>
 </sst>
 </file>
@@ -481,7 +484,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -547,15 +550,15 @@
         <v>8</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>3</v>
@@ -564,7 +567,7 @@
         <v>4</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>12</v>
@@ -587,7 +590,7 @@
         <v>15</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -607,47 +610,67 @@
         <v>18</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="C7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E7" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C7" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>22</v>
-      </c>
       <c r="F7" s="1" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="C8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C8" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E8" s="1" t="s">
+      <c r="B9" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="F8" s="1" t="s">
-        <v>19</v>
+      <c r="C9" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/E/DU6AMKT.xlsx
+++ b/E/DU6AMKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="28">
   <si>
     <t/>
   </si>
   <si>
-    <t>10022534</t>
-  </si>
-  <si>
-    <t>ABC KCP MNS PCH685G</t>
+    <t>20068905</t>
+  </si>
+  <si>
+    <t>FF SKM PUTIH 535G</t>
   </si>
   <si>
     <t>DU6AMKT</t>
@@ -28,67 +28,70 @@
     <t>1</t>
   </si>
   <si>
+    <t>PT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20068906</t>
+  </si>
+  <si>
+    <t>FF SKM COKELAT 535G</t>
+  </si>
+  <si>
+    <t>20138571</t>
+  </si>
+  <si>
+    <t>G/DAY LATTE ORI 10S</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>RT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20138948</t>
+  </si>
+  <si>
+    <t>G/DAY BTRSCOTCH 10S</t>
+  </si>
+  <si>
+    <t>20108264</t>
+  </si>
+  <si>
+    <t>SARI ROTI TAWAR JMBO</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>RT,(E-1H)</t>
+  </si>
+  <si>
+    <t>10003801</t>
+  </si>
+  <si>
+    <t>INDOMI JMB AYM PG127</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
     <t>RT,(E-2B)</t>
   </si>
   <si>
-    <t>10004336</t>
-  </si>
-  <si>
-    <t>INDOMARET AIR MIN600</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>PT,(E-1H)</t>
-  </si>
-  <si>
-    <t>10008882</t>
-  </si>
-  <si>
-    <t>K/API KOPI SPCL 150G</t>
-  </si>
-  <si>
-    <t>RT,(E-4B)</t>
-  </si>
-  <si>
-    <t>20084481</t>
-  </si>
-  <si>
-    <t>POP MIE PD.DWR AYM75</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>20091304</t>
-  </si>
-  <si>
-    <t>POP MIE PD.GLD AYM75</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>20140188</t>
-  </si>
-  <si>
-    <t>POP MI KARI LAVA 79G</t>
+    <t>10003800</t>
+  </si>
+  <si>
+    <t>INDOMI GR SP JUMB129</t>
   </si>
   <si>
     <t>5</t>
   </si>
   <si>
-    <t>20140189</t>
-  </si>
-  <si>
-    <t>POP MI BASO GRNT 77G</t>
-  </si>
-  <si>
-    <t>20024079</t>
-  </si>
-  <si>
-    <t>TELUR AYM NEGERI BKL</t>
+    <t>20130807</t>
+  </si>
+  <si>
+    <t>INDOMIE GRG RNDNG120</t>
   </si>
   <si>
     <t>6</t>
@@ -547,39 +550,39 @@
         <v>4</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>11</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>14</v>
-      </c>
       <c r="C5" s="1" t="s">
         <v>3</v>
       </c>
@@ -587,50 +590,50 @@
         <v>4</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="F6" s="1" t="s">
         <v>17</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="C7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E7" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C7" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E7" s="1" t="s">
+      <c r="F7" s="1" t="s">
         <v>21</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -647,18 +650,18 @@
         <v>4</v>
       </c>
       <c r="E8" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F8" s="1" t="s">
         <v>21</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>3</v>
@@ -667,10 +670,10 @@
         <v>4</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>

--- a/E/DU6AMKT.xlsx
+++ b/E/DU6AMKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="22">
   <si>
     <t/>
   </si>
   <si>
-    <t>20068905</t>
-  </si>
-  <si>
-    <t>FF SKM PUTIH 535G</t>
+    <t>20108264</t>
+  </si>
+  <si>
+    <t>SARI ROTI TAWAR JMBO</t>
   </si>
   <si>
     <t>DU6AMKT</t>
@@ -28,73 +28,55 @@
     <t>1</t>
   </si>
   <si>
-    <t>PT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20068906</t>
-  </si>
-  <si>
-    <t>FF SKM COKELAT 535G</t>
-  </si>
-  <si>
-    <t>20138571</t>
-  </si>
-  <si>
-    <t>G/DAY LATTE ORI 10S</t>
+    <t>RT,(E-1H)</t>
+  </si>
+  <si>
+    <t>10003922</t>
+  </si>
+  <si>
+    <t>ABC KP&amp;GULA+SS.10X30</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
-    <t>RT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20138948</t>
-  </si>
-  <si>
-    <t>G/DAY BTRSCOTCH 10S</t>
-  </si>
-  <si>
-    <t>20108264</t>
-  </si>
-  <si>
-    <t>SARI ROTI TAWAR JMBO</t>
+    <t>RT,(E-4B)</t>
+  </si>
+  <si>
+    <t>10016646</t>
+  </si>
+  <si>
+    <t>INDO/F KECAP MN.R725</t>
   </si>
   <si>
     <t>3</t>
   </si>
   <si>
-    <t>RT,(E-1H)</t>
-  </si>
-  <si>
-    <t>10003801</t>
-  </si>
-  <si>
-    <t>INDOMI JMB AYM PG127</t>
-  </si>
-  <si>
-    <t>4</t>
+    <t>RT,(E-3B)</t>
+  </si>
+  <si>
+    <t>10000185</t>
+  </si>
+  <si>
+    <t>INDOMI KARI AYAM 72G</t>
+  </si>
+  <si>
+    <t>6</t>
   </si>
   <si>
     <t>RT,(E-2B)</t>
   </si>
   <si>
-    <t>10003800</t>
-  </si>
-  <si>
-    <t>INDOMI GR SP JUMB129</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>20130807</t>
-  </si>
-  <si>
-    <t>INDOMIE GRG RNDNG120</t>
-  </si>
-  <si>
-    <t>6</t>
+    <t>10003517</t>
+  </si>
+  <si>
+    <t>INDOMI GORENG SPC 80</t>
+  </si>
+  <si>
+    <t>20074112</t>
+  </si>
+  <si>
+    <t>INDOMIE GRG RICA 85G</t>
   </si>
 </sst>
 </file>
@@ -487,7 +469,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -550,18 +532,18 @@
         <v>4</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>3</v>
@@ -570,18 +552,18 @@
         <v>4</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>3</v>
@@ -590,18 +572,18 @@
         <v>4</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>3</v>
@@ -618,10 +600,10 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>3</v>
@@ -630,50 +612,10 @@
         <v>4</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>

--- a/E/DU6AMKT.xlsx
+++ b/E/DU6AMKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="25">
   <si>
     <t/>
   </si>
   <si>
-    <t>20108264</t>
-  </si>
-  <si>
-    <t>SARI ROTI TAWAR JMBO</t>
+    <t>20031318</t>
+  </si>
+  <si>
+    <t>G/DAY CPUCINO 10X25G</t>
   </si>
   <si>
     <t>DU6AMKT</t>
@@ -28,55 +28,64 @@
     <t>1</t>
   </si>
   <si>
-    <t>RT,(E-1H)</t>
-  </si>
-  <si>
-    <t>10003922</t>
-  </si>
-  <si>
-    <t>ABC KP&amp;GULA+SS.10X30</t>
+    <t>RT,(E-4B)</t>
+  </si>
+  <si>
+    <t>20068905</t>
+  </si>
+  <si>
+    <t>FF SKM PUTIH 535G</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
-    <t>RT,(E-4B)</t>
-  </si>
-  <si>
-    <t>10016646</t>
-  </si>
-  <si>
-    <t>INDO/F KECAP MN.R725</t>
+    <t>PT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20068906</t>
+  </si>
+  <si>
+    <t>FF SKM COKELAT 535G</t>
+  </si>
+  <si>
+    <t>20134968</t>
+  </si>
+  <si>
+    <t>COLLAGENA STERIL189</t>
   </si>
   <si>
     <t>3</t>
   </si>
   <si>
-    <t>RT,(E-3B)</t>
-  </si>
-  <si>
-    <t>10000185</t>
-  </si>
-  <si>
-    <t>INDOMI KARI AYAM 72G</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>RT,(E-2B)</t>
-  </si>
-  <si>
-    <t>10003517</t>
-  </si>
-  <si>
-    <t>INDOMI GORENG SPC 80</t>
-  </si>
-  <si>
-    <t>20074112</t>
-  </si>
-  <si>
-    <t>INDOMIE GRG RICA 85G</t>
+    <t>RT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20101378</t>
+  </si>
+  <si>
+    <t>KODOMO B.WIPE PNK 50</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>20121413</t>
+  </si>
+  <si>
+    <t>KDMO B.WP ALOE 2X50S</t>
+  </si>
+  <si>
+    <t>20139653</t>
+  </si>
+  <si>
+    <t>LRST FAC.TIS 2X200S</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>PT</t>
   </si>
 </sst>
 </file>
@@ -469,7 +478,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -552,18 +561,18 @@
         <v>4</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>3</v>
@@ -572,18 +581,18 @@
         <v>4</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>3</v>
@@ -592,18 +601,18 @@
         <v>4</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>20</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>21</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>3</v>
@@ -612,10 +621,30 @@
         <v>4</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>24</v>
       </c>
     </row>
   </sheetData>

--- a/E/DU6AMKT.xlsx
+++ b/E/DU6AMKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="6">
   <si>
     <t/>
   </si>
   <si>
-    <t>20031318</t>
-  </si>
-  <si>
-    <t>G/DAY CPUCINO 10X25G</t>
+    <t>20141262</t>
+  </si>
+  <si>
+    <t>ELLIPS HS ULT.TR 48</t>
   </si>
   <si>
     <t>DU6AMKT</t>
@@ -28,64 +28,7 @@
     <t>1</t>
   </si>
   <si>
-    <t>RT,(E-4B)</t>
-  </si>
-  <si>
-    <t>20068905</t>
-  </si>
-  <si>
-    <t>FF SKM PUTIH 535G</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>PT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20068906</t>
-  </si>
-  <si>
-    <t>FF SKM COKELAT 535G</t>
-  </si>
-  <si>
-    <t>20134968</t>
-  </si>
-  <si>
-    <t>COLLAGENA STERIL189</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>RT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20101378</t>
-  </si>
-  <si>
-    <t>KODOMO B.WIPE PNK 50</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>20121413</t>
-  </si>
-  <si>
-    <t>KDMO B.WP ALOE 2X50S</t>
-  </si>
-  <si>
-    <t>20139653</t>
-  </si>
-  <si>
-    <t>LRST FAC.TIS 2X200S</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>PT</t>
+    <t>RT,(E-3B)</t>
   </si>
 </sst>
 </file>
@@ -478,11 +421,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
-    <col min="2" max="2" width="22" customWidth="1"/>
+    <col min="2" max="2" width="21" customWidth="1"/>
     <col min="4" max="5" width="3" customWidth="1"/>
     <col min="6" max="6" width="11" customWidth="1"/>
   </cols>
@@ -527,126 +470,6 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/E/DU6AMKT.xlsx
+++ b/E/DU6AMKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="27">
   <si>
     <t/>
   </si>
   <si>
-    <t>20141262</t>
-  </si>
-  <si>
-    <t>ELLIPS HS ULT.TR 48</t>
+    <t>20098168</t>
+  </si>
+  <si>
+    <t>PIKOPI 3IN1 PCK 9'S</t>
   </si>
   <si>
     <t>DU6AMKT</t>
@@ -28,7 +28,70 @@
     <t>1</t>
   </si>
   <si>
-    <t>RT,(E-3B)</t>
+    <t>RT,(E-2B)</t>
+  </si>
+  <si>
+    <t>20068905</t>
+  </si>
+  <si>
+    <t>FF SKM PUTIH 535G</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>PT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20068906</t>
+  </si>
+  <si>
+    <t>FF SKM COKELAT 535G</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>20084481</t>
+  </si>
+  <si>
+    <t>POP MIE PD.DWR AYM75</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>20091304</t>
+  </si>
+  <si>
+    <t>POP MIE PD.GLD AYM75</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>20140188</t>
+  </si>
+  <si>
+    <t>POP MI KARI LAVA 79G</t>
+  </si>
+  <si>
+    <t>20140189</t>
+  </si>
+  <si>
+    <t>POP MI BASO GRNT 77G</t>
+  </si>
+  <si>
+    <t>20096589</t>
+  </si>
+  <si>
+    <t>SEDAAP MIE GRNG 5'S</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>RT,(E-1B)</t>
   </si>
 </sst>
 </file>
@@ -421,11 +484,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
-    <col min="2" max="2" width="21" customWidth="1"/>
+    <col min="2" max="2" width="22" customWidth="1"/>
     <col min="4" max="5" width="3" customWidth="1"/>
     <col min="6" max="6" width="11" customWidth="1"/>
   </cols>
@@ -470,6 +533,146 @@
         <v>5</v>
       </c>
     </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/E/DU6AMKT.xlsx
+++ b/E/DU6AMKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="37">
   <si>
     <t/>
   </si>
   <si>
-    <t>20098168</t>
-  </si>
-  <si>
-    <t>PIKOPI 3IN1 PCK 9'S</t>
+    <t>20086181</t>
+  </si>
+  <si>
+    <t>KAPAL API SPC 20X6G</t>
   </si>
   <si>
     <t>DU6AMKT</t>
@@ -28,70 +28,100 @@
     <t>1</t>
   </si>
   <si>
+    <t>RT,(E-4B)</t>
+  </si>
+  <si>
+    <t>20014069</t>
+  </si>
+  <si>
+    <t>FF UHT FULL CRM 946</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>RT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20014070</t>
+  </si>
+  <si>
+    <t>F/F LOW FAT TPK 946</t>
+  </si>
+  <si>
+    <t>20014071</t>
+  </si>
+  <si>
+    <t>FF UHT CHOCO 946ML</t>
+  </si>
+  <si>
+    <t>20077501</t>
+  </si>
+  <si>
+    <t>FF UHT COCONUT 946</t>
+  </si>
+  <si>
+    <t>20134968</t>
+  </si>
+  <si>
+    <t>COLLAGENA STERIL189</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>20072596</t>
+  </si>
+  <si>
+    <t>SARI ROTI LAPIS BMKH</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>RT,(E-1H)</t>
+  </si>
+  <si>
+    <t>10035954</t>
+  </si>
+  <si>
+    <t>INDOMIE EMPL/GTNG 75</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
     <t>RT,(E-2B)</t>
   </si>
   <si>
-    <t>20068905</t>
-  </si>
-  <si>
-    <t>FF SKM PUTIH 535G</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>PT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20068906</t>
-  </si>
-  <si>
-    <t>FF SKM COKELAT 535G</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>20084481</t>
-  </si>
-  <si>
-    <t>POP MIE PD.DWR AYM75</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>20091304</t>
-  </si>
-  <si>
-    <t>POP MIE PD.GLD AYM75</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>20140188</t>
-  </si>
-  <si>
-    <t>POP MI KARI LAVA 79G</t>
-  </si>
-  <si>
-    <t>20140189</t>
-  </si>
-  <si>
-    <t>POP MI BASO GRNT 77G</t>
-  </si>
-  <si>
-    <t>20096589</t>
-  </si>
-  <si>
-    <t>SEDAAP MIE GRNG 5'S</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>RT,(E-1B)</t>
+    <t>10035955</t>
+  </si>
+  <si>
+    <t>INDOMIE MI KOCOK 75G</t>
+  </si>
+  <si>
+    <t>20019930</t>
+  </si>
+  <si>
+    <t>INDOMIE GRG RNDANG91</t>
+  </si>
+  <si>
+    <t>20085115</t>
+  </si>
+  <si>
+    <t>INDOMI GRNG ACEH 90G</t>
+  </si>
+  <si>
+    <t>20085462</t>
+  </si>
+  <si>
+    <t>INDOMIE SOTO LMNG 80</t>
+  </si>
+  <si>
+    <t>20133372</t>
+  </si>
+  <si>
+    <t>INDOMIE RWN MERCON75</t>
   </si>
 </sst>
 </file>
@@ -484,7 +514,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -567,7 +597,7 @@
         <v>4</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>9</v>
@@ -575,11 +605,11 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>14</v>
-      </c>
       <c r="C5" s="1" t="s">
         <v>3</v>
       </c>
@@ -587,18 +617,18 @@
         <v>4</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>3</v>
@@ -607,18 +637,18 @@
         <v>4</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>3</v>
@@ -630,27 +660,27 @@
         <v>18</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E8" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="F8" s="1" t="s">
         <v>22</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -670,6 +700,106 @@
         <v>25</v>
       </c>
       <c r="F9" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F14" s="1" t="s">
         <v>26</v>
       </c>
     </row>

--- a/E/DU6AMKT.xlsx
+++ b/E/DU6AMKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="34">
   <si>
     <t/>
   </si>
   <si>
-    <t>20086181</t>
-  </si>
-  <si>
-    <t>KAPAL API SPC 20X6G</t>
+    <t>10016646</t>
+  </si>
+  <si>
+    <t>INDO/F KECAP MN.R725</t>
   </si>
   <si>
     <t>DU6AMKT</t>
@@ -28,7 +28,31 @@
     <t>1</t>
   </si>
   <si>
-    <t>RT,(E-4B)</t>
+    <t>RT,(E-3B)</t>
+  </si>
+  <si>
+    <t>20117107</t>
+  </si>
+  <si>
+    <t>BANGO KECAP MNS 735</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>RT,(E-0.5B)</t>
+  </si>
+  <si>
+    <t>10008867</t>
+  </si>
+  <si>
+    <t>SARI/R TAWAR GANDUM</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>RT,(E-1H)</t>
   </si>
   <si>
     <t>20014069</t>
@@ -37,7 +61,7 @@
     <t>FF UHT FULL CRM 946</t>
   </si>
   <si>
-    <t>2</t>
+    <t>4</t>
   </si>
   <si>
     <t>RT,(E-1B)</t>
@@ -61,67 +85,34 @@
     <t>FF UHT COCONUT 946</t>
   </si>
   <si>
-    <t>20134968</t>
-  </si>
-  <si>
-    <t>COLLAGENA STERIL189</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>20072596</t>
-  </si>
-  <si>
-    <t>SARI ROTI LAPIS BMKH</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>RT,(E-1H)</t>
-  </si>
-  <si>
-    <t>10035954</t>
-  </si>
-  <si>
-    <t>INDOMIE EMPL/GTNG 75</t>
-  </si>
-  <si>
-    <t>7</t>
+    <t>20093221</t>
+  </si>
+  <si>
+    <t>INDOMIE GR AYM.GP 85</t>
+  </si>
+  <si>
+    <t>5</t>
   </si>
   <si>
     <t>RT,(E-2B)</t>
   </si>
   <si>
-    <t>10035955</t>
-  </si>
-  <si>
-    <t>INDOMIE MI KOCOK 75G</t>
-  </si>
-  <si>
-    <t>20019930</t>
-  </si>
-  <si>
-    <t>INDOMIE GRG RNDANG91</t>
-  </si>
-  <si>
-    <t>20085115</t>
-  </si>
-  <si>
-    <t>INDOMI GRNG ACEH 90G</t>
-  </si>
-  <si>
-    <t>20085462</t>
-  </si>
-  <si>
-    <t>INDOMIE SOTO LMNG 80</t>
-  </si>
-  <si>
-    <t>20133372</t>
-  </si>
-  <si>
-    <t>INDOMIE RWN MERCON75</t>
+    <t>20101747</t>
+  </si>
+  <si>
+    <t>INDOMI SBLAK HOT/J75</t>
+  </si>
+  <si>
+    <t>20138358</t>
+  </si>
+  <si>
+    <t>INDOMI NYEMK B/LDS80</t>
+  </si>
+  <si>
+    <t>20140632</t>
+  </si>
+  <si>
+    <t>INDOMI NYMEK J/RD 84</t>
   </si>
 </sst>
 </file>
@@ -514,13 +505,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="4" max="5" width="3" customWidth="1"/>
-    <col min="6" max="6" width="11" customWidth="1"/>
+    <col min="6" max="6" width="13" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -597,18 +588,18 @@
         <v>4</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>3</v>
@@ -617,18 +608,18 @@
         <v>4</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>3</v>
@@ -637,38 +628,38 @@
         <v>4</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E7" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="F7" s="1" t="s">
         <v>17</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>3</v>
@@ -677,18 +668,18 @@
         <v>4</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>3</v>
@@ -697,38 +688,38 @@
         <v>4</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F10" s="1" t="s">
         <v>27</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>3</v>
@@ -737,18 +728,18 @@
         <v>4</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>3</v>
@@ -757,50 +748,10 @@
         <v>4</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>

--- a/E/DU6AMKT.xlsx
+++ b/E/DU6AMKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="27">
   <si>
     <t/>
   </si>
   <si>
-    <t>10016646</t>
-  </si>
-  <si>
-    <t>INDO/F KECAP MN.R725</t>
+    <t>20117107</t>
+  </si>
+  <si>
+    <t>BANGO KECAP MNS 735</t>
   </si>
   <si>
     <t>DU6AMKT</t>
@@ -28,37 +28,37 @@
     <t>1</t>
   </si>
   <si>
-    <t>RT,(E-3B)</t>
-  </si>
-  <si>
-    <t>20117107</t>
-  </si>
-  <si>
-    <t>BANGO KECAP MNS 735</t>
+    <t>RT,(E-0.5B)</t>
+  </si>
+  <si>
+    <t>10008867</t>
+  </si>
+  <si>
+    <t>SARI/R TAWAR GANDUM</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
-    <t>RT,(E-0.5B)</t>
-  </si>
-  <si>
-    <t>10008867</t>
-  </si>
-  <si>
-    <t>SARI/R TAWAR GANDUM</t>
+    <t>RT,(E-1H)</t>
+  </si>
+  <si>
+    <t>20031318</t>
+  </si>
+  <si>
+    <t>G/DAY CPUCINO 10X25G</t>
   </si>
   <si>
     <t>3</t>
   </si>
   <si>
-    <t>RT,(E-1H)</t>
-  </si>
-  <si>
-    <t>20014069</t>
-  </si>
-  <si>
-    <t>FF UHT FULL CRM 946</t>
+    <t>RT,(E-4B)</t>
+  </si>
+  <si>
+    <t>20104077</t>
+  </si>
+  <si>
+    <t>SEDAP KCP SPCL 725G</t>
   </si>
   <si>
     <t>4</t>
@@ -67,28 +67,10 @@
     <t>RT,(E-1B)</t>
   </si>
   <si>
-    <t>20014070</t>
-  </si>
-  <si>
-    <t>F/F LOW FAT TPK 946</t>
-  </si>
-  <si>
-    <t>20014071</t>
-  </si>
-  <si>
-    <t>FF UHT CHOCO 946ML</t>
-  </si>
-  <si>
-    <t>20077501</t>
-  </si>
-  <si>
-    <t>FF UHT COCONUT 946</t>
-  </si>
-  <si>
-    <t>20093221</t>
-  </si>
-  <si>
-    <t>INDOMIE GR AYM.GP 85</t>
+    <t>10003800</t>
+  </si>
+  <si>
+    <t>INDOMI GR SP JUMB129</t>
   </si>
   <si>
     <t>5</t>
@@ -97,22 +79,19 @@
     <t>RT,(E-2B)</t>
   </si>
   <si>
-    <t>20101747</t>
-  </si>
-  <si>
-    <t>INDOMI SBLAK HOT/J75</t>
-  </si>
-  <si>
-    <t>20138358</t>
-  </si>
-  <si>
-    <t>INDOMI NYEMK B/LDS80</t>
-  </si>
-  <si>
-    <t>20140632</t>
-  </si>
-  <si>
-    <t>INDOMI NYMEK J/RD 84</t>
+    <t>10003801</t>
+  </si>
+  <si>
+    <t>INDOMI JMB AYM PG127</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>20130807</t>
+  </si>
+  <si>
+    <t>INDOMIE GRG RNDNG120</t>
   </si>
 </sst>
 </file>
@@ -505,7 +484,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -628,18 +607,18 @@
         <v>4</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>3</v>
@@ -648,18 +627,18 @@
         <v>4</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>3</v>
@@ -668,90 +647,10 @@
         <v>4</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>

--- a/E/DU6AMKT.xlsx
+++ b/E/DU6AMKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="30">
   <si>
     <t/>
   </si>
   <si>
-    <t>20117107</t>
-  </si>
-  <si>
-    <t>BANGO KECAP MNS 735</t>
+    <t>20014069</t>
+  </si>
+  <si>
+    <t>FF UHT FULL CRM 946</t>
   </si>
   <si>
     <t>DU6AMKT</t>
@@ -28,70 +28,79 @@
     <t>1</t>
   </si>
   <si>
-    <t>RT,(E-0.5B)</t>
-  </si>
-  <si>
-    <t>10008867</t>
-  </si>
-  <si>
-    <t>SARI/R TAWAR GANDUM</t>
+    <t>RT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20014070</t>
+  </si>
+  <si>
+    <t>F/F LOW FAT TPK 946</t>
+  </si>
+  <si>
+    <t>20014071</t>
+  </si>
+  <si>
+    <t>FF UHT CHOCO 946ML</t>
+  </si>
+  <si>
+    <t>20077501</t>
+  </si>
+  <si>
+    <t>FF UHT COCONUT 946</t>
+  </si>
+  <si>
+    <t>10038932</t>
+  </si>
+  <si>
+    <t>KPL API SPC MIX 10'S</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
-    <t>RT,(E-1H)</t>
-  </si>
-  <si>
-    <t>20031318</t>
-  </si>
-  <si>
-    <t>G/DAY CPUCINO 10X25G</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
     <t>RT,(E-4B)</t>
   </si>
   <si>
-    <t>20104077</t>
-  </si>
-  <si>
-    <t>SEDAP KCP SPCL 725G</t>
+    <t>10003517</t>
+  </si>
+  <si>
+    <t>INDOMI GORENG SPC 80</t>
   </si>
   <si>
     <t>4</t>
   </si>
   <si>
-    <t>RT,(E-1B)</t>
-  </si>
-  <si>
-    <t>10003800</t>
-  </si>
-  <si>
-    <t>INDOMI GR SP JUMB129</t>
+    <t>RT,(E-2B)</t>
+  </si>
+  <si>
+    <t>10000185</t>
+  </si>
+  <si>
+    <t>INDOMI KARI AYAM 72G</t>
   </si>
   <si>
     <t>5</t>
   </si>
   <si>
-    <t>RT,(E-2B)</t>
-  </si>
-  <si>
-    <t>10003801</t>
-  </si>
-  <si>
-    <t>INDOMI JMB AYM PG127</t>
+    <t>20019930</t>
+  </si>
+  <si>
+    <t>INDOMIE GRG RNDANG91</t>
   </si>
   <si>
     <t>6</t>
   </si>
   <si>
-    <t>20130807</t>
-  </si>
-  <si>
-    <t>INDOMIE GRG RNDNG120</t>
+    <t>20074112</t>
+  </si>
+  <si>
+    <t>INDOMIE GRG RICA 85G</t>
+  </si>
+  <si>
+    <t>20085115</t>
+  </si>
+  <si>
+    <t>INDOMI GRNG ACEH 90G</t>
   </si>
 </sst>
 </file>
@@ -484,13 +493,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="4" max="5" width="3" customWidth="1"/>
-    <col min="6" max="6" width="13" customWidth="1"/>
+    <col min="6" max="6" width="11" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -547,18 +556,18 @@
         <v>4</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>3</v>
@@ -567,18 +576,18 @@
         <v>4</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>3</v>
@@ -587,18 +596,18 @@
         <v>4</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>3</v>
@@ -607,18 +616,18 @@
         <v>4</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>3</v>
@@ -627,30 +636,90 @@
         <v>4</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E9" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="F9" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C8" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>21</v>
+      <c r="B10" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>19</v>
       </c>
     </row>
   </sheetData>

--- a/E/DU6AMKT.xlsx
+++ b/E/DU6AMKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="24">
   <si>
     <t/>
   </si>
   <si>
-    <t>20014069</t>
-  </si>
-  <si>
-    <t>FF UHT FULL CRM 946</t>
+    <t>20125856</t>
+  </si>
+  <si>
+    <t>LUWAK KOPI MRN 100G</t>
   </si>
   <si>
     <t>DU6AMKT</t>
@@ -28,79 +28,61 @@
     <t>1</t>
   </si>
   <si>
+    <t>RT,(E-2B)</t>
+  </si>
+  <si>
+    <t>10016646</t>
+  </si>
+  <si>
+    <t>INDO/F KECAP MN.R725</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>RT,(E-3B)</t>
+  </si>
+  <si>
+    <t>20123088</t>
+  </si>
+  <si>
+    <t>SEDAAP KCP MNS 720ML</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
     <t>RT,(E-1B)</t>
   </si>
   <si>
-    <t>20014070</t>
-  </si>
-  <si>
-    <t>F/F LOW FAT TPK 946</t>
-  </si>
-  <si>
-    <t>20014071</t>
-  </si>
-  <si>
-    <t>FF UHT CHOCO 946ML</t>
-  </si>
-  <si>
-    <t>20077501</t>
-  </si>
-  <si>
-    <t>FF UHT COCONUT 946</t>
-  </si>
-  <si>
-    <t>10038932</t>
-  </si>
-  <si>
-    <t>KPL API SPC MIX 10'S</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>RT,(E-4B)</t>
-  </si>
-  <si>
-    <t>10003517</t>
-  </si>
-  <si>
-    <t>INDOMI GORENG SPC 80</t>
+    <t>20027166</t>
+  </si>
+  <si>
+    <t>IDM FAC.TISSUE NP220</t>
   </si>
   <si>
     <t>4</t>
   </si>
   <si>
-    <t>RT,(E-2B)</t>
-  </si>
-  <si>
-    <t>10000185</t>
-  </si>
-  <si>
-    <t>INDOMI KARI AYAM 72G</t>
+    <t>PT</t>
+  </si>
+  <si>
+    <t>20121413</t>
+  </si>
+  <si>
+    <t>KDMO B.WP ALOE 2X50S</t>
   </si>
   <si>
     <t>5</t>
   </si>
   <si>
-    <t>20019930</t>
-  </si>
-  <si>
-    <t>INDOMIE GRG RNDANG91</t>
+    <t>20101378</t>
+  </si>
+  <si>
+    <t>KODOMO B.WIPE PNK 50</t>
   </si>
   <si>
     <t>6</t>
-  </si>
-  <si>
-    <t>20074112</t>
-  </si>
-  <si>
-    <t>INDOMIE GRG RICA 85G</t>
-  </si>
-  <si>
-    <t>20085115</t>
-  </si>
-  <si>
-    <t>INDOMI GRNG ACEH 90G</t>
   </si>
 </sst>
 </file>
@@ -493,7 +475,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -556,18 +538,18 @@
         <v>4</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>3</v>
@@ -576,18 +558,18 @@
         <v>4</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>3</v>
@@ -596,18 +578,18 @@
         <v>4</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>3</v>
@@ -616,18 +598,18 @@
         <v>4</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>3</v>
@@ -636,90 +618,10 @@
         <v>4</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/E/DU6AMKT.xlsx
+++ b/E/DU6AMKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="35">
   <si>
     <t/>
   </si>
   <si>
-    <t>20125856</t>
-  </si>
-  <si>
-    <t>LUWAK KOPI MRN 100G</t>
+    <t>20014070</t>
+  </si>
+  <si>
+    <t>F/F LOW FAT TPK 946</t>
   </si>
   <si>
     <t>DU6AMKT</t>
@@ -28,61 +28,94 @@
     <t>1</t>
   </si>
   <si>
+    <t>RT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20014071</t>
+  </si>
+  <si>
+    <t>FF UHT CHOCO 946ML</t>
+  </si>
+  <si>
+    <t>20077501</t>
+  </si>
+  <si>
+    <t>FF UHT COCONUT 946</t>
+  </si>
+  <si>
+    <t>10000652</t>
+  </si>
+  <si>
+    <t>INDOMI AYAM BWNG 69G</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
     <t>RT,(E-2B)</t>
   </si>
   <si>
-    <t>10016646</t>
-  </si>
-  <si>
-    <t>INDO/F KECAP MN.R725</t>
-  </si>
-  <si>
-    <t>2</t>
+    <t>10004532</t>
+  </si>
+  <si>
+    <t>ENSURE/G VANILLA 800</t>
   </si>
   <si>
     <t>RT,(E-3B)</t>
   </si>
   <si>
-    <t>20123088</t>
-  </si>
-  <si>
-    <t>SEDAAP KCP MNS 720ML</t>
+    <t>20014069</t>
+  </si>
+  <si>
+    <t>FF UHT FULL CRM 946</t>
+  </si>
+  <si>
+    <t>10000184</t>
+  </si>
+  <si>
+    <t>INDOMI AYAM SPECL68G</t>
   </si>
   <si>
     <t>3</t>
   </si>
   <si>
-    <t>RT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20027166</t>
-  </si>
-  <si>
-    <t>IDM FAC.TISSUE NP220</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>PT</t>
-  </si>
-  <si>
-    <t>20121413</t>
-  </si>
-  <si>
-    <t>KDMO B.WP ALOE 2X50S</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>20101378</t>
-  </si>
-  <si>
-    <t>KODOMO B.WIPE PNK 50</t>
-  </si>
-  <si>
-    <t>6</t>
+    <t>10000713</t>
+  </si>
+  <si>
+    <t>INDOMI KLD AYAM 75G</t>
+  </si>
+  <si>
+    <t>10002560</t>
+  </si>
+  <si>
+    <t>INDOMI SOTO MIE 70GR</t>
+  </si>
+  <si>
+    <t>20007834</t>
+  </si>
+  <si>
+    <t>INDOMIE SOTO SPCL 75</t>
+  </si>
+  <si>
+    <t>20137101</t>
+  </si>
+  <si>
+    <t>INDOMIE SOTO PD.D 76</t>
+  </si>
+  <si>
+    <t>20137102</t>
+  </si>
+  <si>
+    <t>INDOMIE SOTO KN 76G</t>
+  </si>
+  <si>
+    <t>20141862</t>
+  </si>
+  <si>
+    <t>SR RT GANDUM KPS 200</t>
+  </si>
+  <si>
+    <t>RT,(E-1H)</t>
   </si>
 </sst>
 </file>
@@ -475,7 +508,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -538,18 +571,18 @@
         <v>4</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>3</v>
@@ -558,18 +591,18 @@
         <v>4</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>3</v>
@@ -578,18 +611,18 @@
         <v>4</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>3</v>
@@ -598,30 +631,170 @@
         <v>4</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E8" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="F8" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C7" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E7" s="1" t="s">
+      <c r="B9" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="F7" s="1" t="s">
+      <c r="C9" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F9" s="1" t="s">
         <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>34</v>
       </c>
     </row>
   </sheetData>

--- a/E/DU6AMKT.xlsx
+++ b/E/DU6AMKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="22">
   <si>
     <t/>
   </si>
   <si>
-    <t>20014070</t>
-  </si>
-  <si>
-    <t>F/F LOW FAT TPK 946</t>
+    <t>20035998</t>
+  </si>
+  <si>
+    <t>IDM TRVL PACK 50'S</t>
   </si>
   <si>
     <t>DU6AMKT</t>
@@ -28,94 +28,55 @@
     <t>1</t>
   </si>
   <si>
+    <t>PT</t>
+  </si>
+  <si>
+    <t>20021393</t>
+  </si>
+  <si>
+    <t>MAMY/P PANT STD XL</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>20127047</t>
+  </si>
+  <si>
+    <t>MR.BRD S.CHSE 135 G</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>RT,(E-1H)</t>
+  </si>
+  <si>
+    <t>20139188</t>
+  </si>
+  <si>
+    <t>MR.BRD S.SRKYA 135 G</t>
+  </si>
+  <si>
+    <t>20136705</t>
+  </si>
+  <si>
+    <t>MR.BRD S.CHOCO 135 G</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>20096499</t>
+  </si>
+  <si>
+    <t>SMYANG AYM CBO 130 G</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
     <t>RT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20014071</t>
-  </si>
-  <si>
-    <t>FF UHT CHOCO 946ML</t>
-  </si>
-  <si>
-    <t>20077501</t>
-  </si>
-  <si>
-    <t>FF UHT COCONUT 946</t>
-  </si>
-  <si>
-    <t>10000652</t>
-  </si>
-  <si>
-    <t>INDOMI AYAM BWNG 69G</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>RT,(E-2B)</t>
-  </si>
-  <si>
-    <t>10004532</t>
-  </si>
-  <si>
-    <t>ENSURE/G VANILLA 800</t>
-  </si>
-  <si>
-    <t>RT,(E-3B)</t>
-  </si>
-  <si>
-    <t>20014069</t>
-  </si>
-  <si>
-    <t>FF UHT FULL CRM 946</t>
-  </si>
-  <si>
-    <t>10000184</t>
-  </si>
-  <si>
-    <t>INDOMI AYAM SPECL68G</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>10000713</t>
-  </si>
-  <si>
-    <t>INDOMI KLD AYAM 75G</t>
-  </si>
-  <si>
-    <t>10002560</t>
-  </si>
-  <si>
-    <t>INDOMI SOTO MIE 70GR</t>
-  </si>
-  <si>
-    <t>20007834</t>
-  </si>
-  <si>
-    <t>INDOMIE SOTO SPCL 75</t>
-  </si>
-  <si>
-    <t>20137101</t>
-  </si>
-  <si>
-    <t>INDOMIE SOTO PD.D 76</t>
-  </si>
-  <si>
-    <t>20137102</t>
-  </si>
-  <si>
-    <t>INDOMIE SOTO KN 76G</t>
-  </si>
-  <si>
-    <t>20141862</t>
-  </si>
-  <si>
-    <t>SR RT GANDUM KPS 200</t>
-  </si>
-  <si>
-    <t>RT,(E-1H)</t>
   </si>
 </sst>
 </file>
@@ -508,7 +469,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -571,7 +532,7 @@
         <v>4</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>5</v>
@@ -579,10 +540,10 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>3</v>
@@ -591,18 +552,18 @@
         <v>4</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>3</v>
@@ -611,18 +572,18 @@
         <v>4</v>
       </c>
       <c r="E5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F5" s="1" t="s">
         <v>12</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>3</v>
@@ -631,18 +592,18 @@
         <v>4</v>
       </c>
       <c r="E6" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F6" s="1" t="s">
         <v>12</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>3</v>
@@ -651,150 +612,10 @@
         <v>4</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E8" s="1" t="s">
         <v>21</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>34</v>
       </c>
     </row>
   </sheetData>

--- a/E/DU6AMKT.xlsx
+++ b/E/DU6AMKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="28">
   <si>
     <t/>
   </si>
   <si>
-    <t>20035998</t>
-  </si>
-  <si>
-    <t>IDM TRVL PACK 50'S</t>
+    <t>10003974</t>
+  </si>
+  <si>
+    <t>TROPICAL MNYK BTL 2L</t>
   </si>
   <si>
     <t>DU6AMKT</t>
@@ -28,55 +28,73 @@
     <t>1</t>
   </si>
   <si>
-    <t>PT</t>
-  </si>
-  <si>
-    <t>20021393</t>
-  </si>
-  <si>
-    <t>MAMY/P PANT STD XL</t>
+    <t>RT,(E-4B)</t>
+  </si>
+  <si>
+    <t>20117107</t>
+  </si>
+  <si>
+    <t>BANGO KECAP MNS 735</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
-    <t>20127047</t>
-  </si>
-  <si>
-    <t>MR.BRD S.CHSE 135 G</t>
+    <t>RT,(E-0.5B)</t>
+  </si>
+  <si>
+    <t>20031318</t>
+  </si>
+  <si>
+    <t>G/DAY CPUCINO 10X25G</t>
   </si>
   <si>
     <t>3</t>
   </si>
   <si>
-    <t>RT,(E-1H)</t>
-  </si>
-  <si>
-    <t>20139188</t>
-  </si>
-  <si>
-    <t>MR.BRD S.SRKYA 135 G</t>
-  </si>
-  <si>
-    <t>20136705</t>
-  </si>
-  <si>
-    <t>MR.BRD S.CHOCO 135 G</t>
+    <t>10023789</t>
+  </si>
+  <si>
+    <t>SEDAAP MIE GORENG 91</t>
   </si>
   <si>
     <t>4</t>
   </si>
   <si>
-    <t>20096499</t>
-  </si>
-  <si>
-    <t>SMYANG AYM CBO 130 G</t>
+    <t>RT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20096781</t>
+  </si>
+  <si>
+    <t>SEDAAP MI KR.SPCY 87</t>
+  </si>
+  <si>
+    <t>20125555</t>
+  </si>
+  <si>
+    <t>SEDAP MI KRN CH/BL86</t>
+  </si>
+  <si>
+    <t>20136385</t>
+  </si>
+  <si>
+    <t>SEDAAP GRG CHF.DVN93</t>
   </si>
   <si>
     <t>5</t>
   </si>
   <si>
-    <t>RT,(E-1B)</t>
+    <t>20104117</t>
+  </si>
+  <si>
+    <t>MR.BRD SISIR COKELAT</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>RT</t>
   </si>
 </sst>
 </file>
@@ -469,13 +487,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="4" max="5" width="3" customWidth="1"/>
-    <col min="6" max="6" width="11" customWidth="1"/>
+    <col min="6" max="6" width="13" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -535,15 +553,15 @@
         <v>8</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>3</v>
@@ -552,10 +570,10 @@
         <v>4</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -572,38 +590,38 @@
         <v>4</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="F6" s="1" t="s">
         <v>16</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>3</v>
@@ -612,10 +630,50 @@
         <v>4</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F7" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
         <v>21</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>27</v>
       </c>
     </row>
   </sheetData>

--- a/E/DU6AMKT.xlsx
+++ b/E/DU6AMKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="29">
   <si>
     <t/>
   </si>
   <si>
-    <t>10003974</t>
-  </si>
-  <si>
-    <t>TROPICAL MNYK BTL 2L</t>
+    <t>20016512</t>
+  </si>
+  <si>
+    <t>SUNCO MNYK GORENG 2L</t>
   </si>
   <si>
     <t>DU6AMKT</t>
@@ -31,70 +31,73 @@
     <t>RT,(E-4B)</t>
   </si>
   <si>
-    <t>20117107</t>
-  </si>
-  <si>
-    <t>BANGO KECAP MNS 735</t>
+    <t>20125856</t>
+  </si>
+  <si>
+    <t>LUWAK KOPI MRN 100G</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
-    <t>RT,(E-0.5B)</t>
-  </si>
-  <si>
-    <t>20031318</t>
-  </si>
-  <si>
-    <t>G/DAY CPUCINO 10X25G</t>
+    <t>RT,(E-2B)</t>
+  </si>
+  <si>
+    <t>20101825</t>
+  </si>
+  <si>
+    <t>VDRAN XMRT1+ MDU 900</t>
   </si>
   <si>
     <t>3</t>
   </si>
   <si>
-    <t>10023789</t>
-  </si>
-  <si>
-    <t>SEDAAP MIE GORENG 91</t>
+    <t>20113346</t>
+  </si>
+  <si>
+    <t>VDRAN XMRT1+ VAN 900</t>
+  </si>
+  <si>
+    <t>10003517</t>
+  </si>
+  <si>
+    <t>INDOMI GORENG SPC 80</t>
   </si>
   <si>
     <t>4</t>
   </si>
   <si>
+    <t>20019930</t>
+  </si>
+  <si>
+    <t>INDOMIE GRG RNDANG91</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>20085115</t>
+  </si>
+  <si>
+    <t>INDOMI GRNG ACEH 90G</t>
+  </si>
+  <si>
+    <t>20096590</t>
+  </si>
+  <si>
+    <t>SEDAAP MIE SOTO 5'S</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
     <t>RT,(E-1B)</t>
   </si>
   <si>
-    <t>20096781</t>
-  </si>
-  <si>
-    <t>SEDAAP MI KR.SPCY 87</t>
-  </si>
-  <si>
-    <t>20125555</t>
-  </si>
-  <si>
-    <t>SEDAP MI KRN CH/BL86</t>
-  </si>
-  <si>
-    <t>20136385</t>
-  </si>
-  <si>
-    <t>SEDAAP GRG CHF.DVN93</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>20104117</t>
-  </si>
-  <si>
-    <t>MR.BRD SISIR COKELAT</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>RT</t>
+    <t>20140674</t>
+  </si>
+  <si>
+    <t>SEDAAP AYM BWG 5'S</t>
   </si>
 </sst>
 </file>
@@ -487,13 +490,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="4" max="5" width="3" customWidth="1"/>
-    <col min="6" max="6" width="13" customWidth="1"/>
+    <col min="6" max="6" width="11" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -573,7 +576,7 @@
         <v>12</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -590,50 +593,50 @@
         <v>4</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B6" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>15</v>
-      </c>
       <c r="F6" s="1" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="C7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E7" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C7" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>15</v>
-      </c>
       <c r="F7" s="1" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -650,30 +653,50 @@
         <v>4</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="C9" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E9" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C9" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E9" s="1" t="s">
+      <c r="F9" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="F9" s="1" t="s">
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
         <v>27</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>26</v>
       </c>
     </row>
   </sheetData>

--- a/E/DU6AMKT.xlsx
+++ b/E/DU6AMKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="20">
   <si>
     <t/>
   </si>
   <si>
-    <t>20016512</t>
-  </si>
-  <si>
-    <t>SUNCO MNYK GORENG 2L</t>
+    <t>20067868</t>
+  </si>
+  <si>
+    <t>LUWAK KOPI+GULA 5'S</t>
   </si>
   <si>
     <t>DU6AMKT</t>
@@ -28,76 +28,49 @@
     <t>1</t>
   </si>
   <si>
-    <t>RT,(E-4B)</t>
-  </si>
-  <si>
-    <t>20125856</t>
-  </si>
-  <si>
-    <t>LUWAK KOPI MRN 100G</t>
+    <t>RT,(E-2B)</t>
+  </si>
+  <si>
+    <t>20131625</t>
+  </si>
+  <si>
+    <t>LARISST FCL.TIS 250S</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
-    <t>RT,(E-2B)</t>
-  </si>
-  <si>
-    <t>20101825</t>
-  </si>
-  <si>
-    <t>VDRAN XMRT1+ MDU 900</t>
+    <t>PT,(E-4B)</t>
+  </si>
+  <si>
+    <t>20104117</t>
+  </si>
+  <si>
+    <t>MR.BRD SISIR COKELAT</t>
   </si>
   <si>
     <t>3</t>
   </si>
   <si>
-    <t>20113346</t>
-  </si>
-  <si>
-    <t>VDRAN XMRT1+ VAN 900</t>
-  </si>
-  <si>
-    <t>10003517</t>
-  </si>
-  <si>
-    <t>INDOMI GORENG SPC 80</t>
+    <t>RT</t>
+  </si>
+  <si>
+    <t>10000713</t>
+  </si>
+  <si>
+    <t>INDOMI KLD AYAM 75G</t>
   </si>
   <si>
     <t>4</t>
   </si>
   <si>
-    <t>20019930</t>
-  </si>
-  <si>
-    <t>INDOMIE GRG RNDANG91</t>
+    <t>10002560</t>
+  </si>
+  <si>
+    <t>INDOMI SOTO MIE 70GR</t>
   </si>
   <si>
     <t>5</t>
-  </si>
-  <si>
-    <t>20085115</t>
-  </si>
-  <si>
-    <t>INDOMI GRNG ACEH 90G</t>
-  </si>
-  <si>
-    <t>20096590</t>
-  </si>
-  <si>
-    <t>SEDAAP MIE SOTO 5'S</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>RT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20140674</t>
-  </si>
-  <si>
-    <t>SEDAAP AYM BWG 5'S</t>
   </si>
 </sst>
 </file>
@@ -490,16 +463,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="4" max="5" width="3" customWidth="1"/>
-    <col min="6" max="6" width="11" customWidth="1"/>
+    <col min="6" max="7" width="10" customWidth="1"/>
+    <col min="8" max="8" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -518,8 +492,14 @@
       <c r="F1" s="1" t="s">
         <v>0</v>
       </c>
+      <c r="G1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>0</v>
+      </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -535,11 +515,11 @@
       <c r="E2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
@@ -555,11 +535,11 @@
       <c r="E3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="H3" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>10</v>
       </c>
@@ -575,16 +555,16 @@
       <c r="E4" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F4" s="1" t="s">
-        <v>9</v>
+      <c r="H4" s="1" t="s">
+        <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>3</v>
@@ -593,18 +573,18 @@
         <v>4</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>9</v>
+        <v>16</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>3</v>
@@ -613,90 +593,10 @@
         <v>4</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B7" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C7" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>26</v>
+      <c r="H6" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/E/DU6AMKT.xlsx
+++ b/E/DU6AMKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="32">
   <si>
     <t/>
   </si>
   <si>
-    <t>20067868</t>
-  </si>
-  <si>
-    <t>LUWAK KOPI+GULA 5'S</t>
+    <t>20094283</t>
+  </si>
+  <si>
+    <t>INDOMILK KM PTH 535G</t>
   </si>
   <si>
     <t>DU6AMKT</t>
@@ -28,49 +28,85 @@
     <t>1</t>
   </si>
   <si>
+    <t>RT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20120855</t>
+  </si>
+  <si>
+    <t>INDOMILK SWIS CHO535</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>10004906</t>
+  </si>
+  <si>
+    <t>BEAR BRAND STERIL189</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>20140174</t>
+  </si>
+  <si>
+    <t>BEAR BRAND CLGEN 189</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>10000975</t>
+  </si>
+  <si>
+    <t>POP MIE AYAM 75G</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
     <t>RT,(E-2B)</t>
   </si>
   <si>
-    <t>20131625</t>
-  </si>
-  <si>
-    <t>LARISST FCL.TIS 250S</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>PT,(E-4B)</t>
-  </si>
-  <si>
-    <t>20104117</t>
-  </si>
-  <si>
-    <t>MR.BRD SISIR COKELAT</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>RT</t>
-  </si>
-  <si>
-    <t>10000713</t>
-  </si>
-  <si>
-    <t>INDOMI KLD AYAM 75G</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>10002560</t>
-  </si>
-  <si>
-    <t>INDOMI SOTO MIE 70GR</t>
-  </si>
-  <si>
-    <t>5</t>
+    <t>10000861</t>
+  </si>
+  <si>
+    <t>POP MIE BASO 75G</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>10014292</t>
+  </si>
+  <si>
+    <t>POP MIE KRI AYM 75G</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>10014293</t>
+  </si>
+  <si>
+    <t>POP MIE SOTO AYM 75G</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>20087155</t>
+  </si>
+  <si>
+    <t>POP MIE AYM BWG 75G</t>
+  </si>
+  <si>
+    <t>20136587</t>
+  </si>
+  <si>
+    <t>POP MI INDOMIE GR 80</t>
   </si>
 </sst>
 </file>
@@ -463,17 +499,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="4" max="5" width="3" customWidth="1"/>
-    <col min="6" max="7" width="10" customWidth="1"/>
-    <col min="8" max="8" width="11" customWidth="1"/>
+    <col min="6" max="6" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -492,14 +527,8 @@
       <c r="F1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -515,11 +544,11 @@
       <c r="E2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
@@ -535,68 +564,168 @@
       <c r="E3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="F3" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
+      <c r="B4" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="C4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E4" s="1" t="s">
+      <c r="F4" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="B5" s="1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
+      <c r="C5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="F5" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E5" s="1" t="s">
+      <c r="B6" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="H5" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
+      <c r="C6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="F6" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C6" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E6" s="1" t="s">
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="H6" s="1" t="s">
-        <v>5</v>
+      <c r="B7" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
   </sheetData>

--- a/E/DU6AMKT.xlsx
+++ b/E/DU6AMKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="33">
   <si>
     <t/>
   </si>
   <si>
-    <t>20094283</t>
-  </si>
-  <si>
-    <t>INDOMILK KM PTH 535G</t>
+    <t>20074147</t>
+  </si>
+  <si>
+    <t>SGM EKSPL1+ MADU 600</t>
   </si>
   <si>
     <t>DU6AMKT</t>
@@ -28,85 +28,88 @@
     <t>1</t>
   </si>
   <si>
+    <t>RT,(E-2B)</t>
+  </si>
+  <si>
+    <t>20077508</t>
+  </si>
+  <si>
+    <t>SGM EKSPL1+ VAN 600G</t>
+  </si>
+  <si>
+    <t>20083795</t>
+  </si>
+  <si>
+    <t>F/FLAG UHT CHO 6X110</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
     <t>RT,(E-1B)</t>
   </si>
   <si>
-    <t>20120855</t>
-  </si>
-  <si>
-    <t>INDOMILK SWIS CHO535</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>10004906</t>
-  </si>
-  <si>
-    <t>BEAR BRAND STERIL189</t>
+    <t>20091183</t>
+  </si>
+  <si>
+    <t>F/FLAG UHT STR 6X110</t>
+  </si>
+  <si>
+    <t>20127047</t>
+  </si>
+  <si>
+    <t>MR.BRD SBK SOFT CHSE</t>
   </si>
   <si>
     <t>3</t>
   </si>
   <si>
-    <t>20140174</t>
-  </si>
-  <si>
-    <t>BEAR BRAND CLGEN 189</t>
+    <t>RT,(E-1H)</t>
+  </si>
+  <si>
+    <t>20136705</t>
+  </si>
+  <si>
+    <t>MR.BREAD SOFT CHOCO</t>
+  </si>
+  <si>
+    <t>20139188</t>
+  </si>
+  <si>
+    <t>MR.BREAD SOFT SRKAYA</t>
+  </si>
+  <si>
+    <t>10003801</t>
+  </si>
+  <si>
+    <t>INDOMI JMB AYM PG127</t>
   </si>
   <si>
     <t>4</t>
   </si>
   <si>
-    <t>10000975</t>
-  </si>
-  <si>
-    <t>POP MIE AYAM 75G</t>
+    <t>10003800</t>
+  </si>
+  <si>
+    <t>INDOMI GR SP JUMB129</t>
   </si>
   <si>
     <t>5</t>
   </si>
   <si>
-    <t>RT,(E-2B)</t>
-  </si>
-  <si>
-    <t>10000861</t>
-  </si>
-  <si>
-    <t>POP MIE BASO 75G</t>
+    <t>20130807</t>
+  </si>
+  <si>
+    <t>INDOMIE GRG RNDNG120</t>
   </si>
   <si>
     <t>6</t>
   </si>
   <si>
-    <t>10014292</t>
-  </si>
-  <si>
-    <t>POP MIE KRI AYM 75G</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>10014293</t>
-  </si>
-  <si>
-    <t>POP MIE SOTO AYM 75G</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>20087155</t>
-  </si>
-  <si>
-    <t>POP MIE AYM BWG 75G</t>
-  </si>
-  <si>
-    <t>20136587</t>
-  </si>
-  <si>
-    <t>POP MI INDOMIE GR 80</t>
+    <t>20142599</t>
+  </si>
+  <si>
+    <t>INDOMI GR CB.IJO 120</t>
   </si>
 </sst>
 </file>
@@ -499,7 +502,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -562,7 +565,7 @@
         <v>4</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>5</v>
@@ -570,22 +573,22 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="C4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E4" s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>11</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -602,39 +605,39 @@
         <v>4</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="C6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C6" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E6" s="1" t="s">
+      <c r="F6" s="1" t="s">
         <v>17</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B7" s="1" t="s">
-        <v>20</v>
-      </c>
       <c r="C7" s="1" t="s">
         <v>3</v>
       </c>
@@ -642,18 +645,18 @@
         <v>4</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>3</v>
@@ -662,18 +665,18 @@
         <v>4</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>3</v>
@@ -682,18 +685,18 @@
         <v>4</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>18</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>3</v>
@@ -705,27 +708,47 @@
         <v>27</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>18</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E11" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="F11" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C11" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>18</v>
+      <c r="B12" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/E/DU6AMKT.xlsx
+++ b/E/DU6AMKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="37">
   <si>
     <t/>
   </si>
   <si>
-    <t>20074147</t>
-  </si>
-  <si>
-    <t>SGM EKSPL1+ MADU 600</t>
+    <t>20084481</t>
+  </si>
+  <si>
+    <t>P/MIE P.DWR SQDAYM75</t>
   </si>
   <si>
     <t>DU6AMKT</t>
@@ -31,85 +31,97 @@
     <t>RT,(E-2B)</t>
   </si>
   <si>
-    <t>20077508</t>
-  </si>
-  <si>
-    <t>SGM EKSPL1+ VAN 600G</t>
-  </si>
-  <si>
-    <t>20083795</t>
-  </si>
-  <si>
-    <t>F/FLAG UHT CHO 6X110</t>
+    <t>20091304</t>
+  </si>
+  <si>
+    <t>P/MIE GRG P.GLD AY75</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
+    <t>20140188</t>
+  </si>
+  <si>
+    <t>POP MI KARI LAVA 79G</t>
+  </si>
+  <si>
+    <t>20140189</t>
+  </si>
+  <si>
+    <t>POP MI BASO GRNT 77G</t>
+  </si>
+  <si>
+    <t>20096589</t>
+  </si>
+  <si>
+    <t>SEDAAP MIE GRNG 5'S</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
     <t>RT,(E-1B)</t>
   </si>
   <si>
-    <t>20091183</t>
-  </si>
-  <si>
-    <t>F/FLAG UHT STR 6X110</t>
-  </si>
-  <si>
-    <t>20127047</t>
-  </si>
-  <si>
-    <t>MR.BRD SBK SOFT CHSE</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>RT,(E-1H)</t>
-  </si>
-  <si>
-    <t>20136705</t>
-  </si>
-  <si>
-    <t>MR.BREAD SOFT CHOCO</t>
-  </si>
-  <si>
-    <t>20139188</t>
-  </si>
-  <si>
-    <t>MR.BREAD SOFT SRKAYA</t>
-  </si>
-  <si>
-    <t>10003801</t>
-  </si>
-  <si>
-    <t>INDOMI JMB AYM PG127</t>
+    <t>20016512</t>
+  </si>
+  <si>
+    <t>SUNCO MNYK GORENG 2L</t>
   </si>
   <si>
     <t>4</t>
   </si>
   <si>
-    <t>10003800</t>
-  </si>
-  <si>
-    <t>INDOMI GR SP JUMB129</t>
+    <t>RT,(E-4B)</t>
+  </si>
+  <si>
+    <t>20014069</t>
+  </si>
+  <si>
+    <t>FF UHT FULL CRM 946</t>
   </si>
   <si>
     <t>5</t>
   </si>
   <si>
-    <t>20130807</t>
-  </si>
-  <si>
-    <t>INDOMIE GRG RNDNG120</t>
+    <t>20014070</t>
+  </si>
+  <si>
+    <t>F/F LOW FAT TPK 946</t>
+  </si>
+  <si>
+    <t>20014071</t>
+  </si>
+  <si>
+    <t>FF UHT CHOCO 946ML</t>
+  </si>
+  <si>
+    <t>20077501</t>
+  </si>
+  <si>
+    <t>FF UHT COCONUT 946</t>
+  </si>
+  <si>
+    <t>20068905</t>
+  </si>
+  <si>
+    <t>FF SKM PUTIH 535G</t>
   </si>
   <si>
     <t>6</t>
   </si>
   <si>
-    <t>20142599</t>
-  </si>
-  <si>
-    <t>INDOMI GR CB.IJO 120</t>
+    <t>PT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20068906</t>
+  </si>
+  <si>
+    <t>FF SKM COKELAT 535G</t>
+  </si>
+  <si>
+    <t>7</t>
   </si>
 </sst>
 </file>
@@ -502,7 +514,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -565,7 +577,7 @@
         <v>4</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>5</v>
@@ -573,31 +585,31 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>10</v>
-      </c>
       <c r="F4" s="1" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>13</v>
-      </c>
       <c r="C5" s="1" t="s">
         <v>3</v>
       </c>
@@ -605,58 +617,58 @@
         <v>4</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="C6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C6" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E6" s="1" t="s">
+      <c r="F6" s="1" t="s">
         <v>16</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="C7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E7" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C7" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>16</v>
-      </c>
       <c r="F7" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>3</v>
@@ -665,38 +677,38 @@
         <v>4</v>
       </c>
       <c r="E8" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F8" s="1" t="s">
         <v>16</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B9" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E9" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C9" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>24</v>
-      </c>
       <c r="F9" s="1" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>3</v>
@@ -705,10 +717,10 @@
         <v>4</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -725,30 +737,50 @@
         <v>4</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B12" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="C12" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E12" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C12" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>30</v>
-      </c>
       <c r="F12" s="1" t="s">
-        <v>5</v>
+        <v>33</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>33</v>
       </c>
     </row>
   </sheetData>

--- a/E/DU6AMKT.xlsx
+++ b/E/DU6AMKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="42">
   <si>
     <t/>
   </si>
   <si>
-    <t>20127047</t>
-  </si>
-  <si>
-    <t>MR.BRD SBK SOFT CHSE</t>
+    <t>20070110</t>
+  </si>
+  <si>
+    <t>VDORAN XMRT1+ MDU700</t>
   </si>
   <si>
     <t>DU6AMKT</t>
@@ -28,25 +28,19 @@
     <t>1</t>
   </si>
   <si>
-    <t>RT,(E-1H)</t>
-  </si>
-  <si>
-    <t>20136705</t>
-  </si>
-  <si>
-    <t>MR.BREAD SOFT CHOCO</t>
-  </si>
-  <si>
-    <t>20139188</t>
-  </si>
-  <si>
-    <t>MR.BREAD SOFT SRKAYA</t>
-  </si>
-  <si>
-    <t>20014069</t>
-  </si>
-  <si>
-    <t>FF UHT FULL CRM 946</t>
+    <t>RT,(E-2B)</t>
+  </si>
+  <si>
+    <t>20090042</t>
+  </si>
+  <si>
+    <t>VDORAN XMRT1+ VAN700</t>
+  </si>
+  <si>
+    <t>20046081</t>
+  </si>
+  <si>
+    <t>G/D 3IN1 MCCINO 10'S</t>
   </si>
   <si>
     <t>2</t>
@@ -55,67 +49,94 @@
     <t>RT,(E-1B)</t>
   </si>
   <si>
-    <t>20014070</t>
-  </si>
-  <si>
-    <t>F/F LOW FAT TPK 946</t>
-  </si>
-  <si>
-    <t>20014071</t>
-  </si>
-  <si>
-    <t>FF UHT CHOCO 946ML</t>
-  </si>
-  <si>
-    <t>20077501</t>
-  </si>
-  <si>
-    <t>FF UHT COCONUT 946</t>
-  </si>
-  <si>
-    <t>10025006</t>
-  </si>
-  <si>
-    <t>NESTLE KOKO.COMBO 30</t>
+    <t>20060370</t>
+  </si>
+  <si>
+    <t>G/DAY CHOCOCINO 10'S</t>
+  </si>
+  <si>
+    <t>20060371</t>
+  </si>
+  <si>
+    <t>G/DAY VNL.LATTE 10'S</t>
+  </si>
+  <si>
+    <t>20049556</t>
+  </si>
+  <si>
+    <t>SEDAAP MIE AYM KR 88</t>
   </si>
   <si>
     <t>3</t>
   </si>
   <si>
-    <t>10003801</t>
-  </si>
-  <si>
-    <t>INDOMI JMB AYM PG127</t>
+    <t>20096781</t>
+  </si>
+  <si>
+    <t>SEDAAP MI KR.SPCY 87</t>
+  </si>
+  <si>
+    <t>20125555</t>
+  </si>
+  <si>
+    <t>SEDAP MI KRN CH/BL86</t>
+  </si>
+  <si>
+    <t>20136385</t>
+  </si>
+  <si>
+    <t>SEDAAP GRG CHF.DVN93</t>
+  </si>
+  <si>
+    <t>10000652</t>
+  </si>
+  <si>
+    <t>INDOMI AYAM BWNG 69G</t>
   </si>
   <si>
     <t>4</t>
   </si>
   <si>
-    <t>RT,(E-2B)</t>
-  </si>
-  <si>
-    <t>20142599</t>
-  </si>
-  <si>
-    <t>INDOMI GR CB.IJO 120</t>
+    <t>20137102</t>
+  </si>
+  <si>
+    <t>INDOMIE SOTO KN 76G</t>
   </si>
   <si>
     <t>5</t>
   </si>
   <si>
-    <t>10003800</t>
-  </si>
-  <si>
-    <t>INDOMI GR SP JUMB129</t>
+    <t>10000184</t>
+  </si>
+  <si>
+    <t>INDOMI AYAM SPECL68G</t>
   </si>
   <si>
     <t>6</t>
   </si>
   <si>
-    <t>20130807</t>
-  </si>
-  <si>
-    <t>INDOMIE GRG RNDNG120</t>
+    <t>10000713</t>
+  </si>
+  <si>
+    <t>INDOMI KLD AYAM 75G</t>
+  </si>
+  <si>
+    <t>10002560</t>
+  </si>
+  <si>
+    <t>INDOMI SOTO MIE 70GR</t>
+  </si>
+  <si>
+    <t>20007834</t>
+  </si>
+  <si>
+    <t>INDOMIE SOTO SPCL 75</t>
+  </si>
+  <si>
+    <t>20137101</t>
+  </si>
+  <si>
+    <t>INDOMIE SOTO PD.D 76</t>
   </si>
 </sst>
 </file>
@@ -508,7 +529,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -591,30 +612,30 @@
         <v>4</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="F5" s="1" t="s">
         <v>11</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -631,10 +652,10 @@
         <v>4</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -651,38 +672,38 @@
         <v>4</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E8" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B8" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>12</v>
-      </c>
       <c r="F8" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>3</v>
@@ -691,10 +712,10 @@
         <v>4</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -711,70 +732,150 @@
         <v>4</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>26</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E11" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B11" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="F11" s="1" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E12" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B12" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>32</v>
-      </c>
       <c r="F12" s="1" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E13" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="F13" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="C13" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>26</v>
+      <c r="B14" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
